--- a/output/executive_summary.xlsx
+++ b/output/executive_summary.xlsx
@@ -626,9 +626,9 @@
           <t>7.6%</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>5.0%</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -636,17 +636,17 @@
           <t>4.4%</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2.8%</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>3.3%</t>
         </is>
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>€3,240 m</t>
+          <t>€5,340 m</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>€2,000 m</t>
+          <t>€6,662 m</t>
         </is>
       </c>
     </row>
@@ -695,14 +695,14 @@
           <t>Net Liquidity / liquidity indicator</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>€44,862 m</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>€44,862 m</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -752,9 +752,9 @@
           <t>12.9%</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>4.8%</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -816,9 +816,9 @@
           <t>€2.68</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>€5.34</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -843,14 +843,14 @@
           <t>Dividend per Share</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>€4.40</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Reported</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Reported</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Reported</t>
         </is>
       </c>
     </row>
@@ -880,29 +880,29 @@
           <t>Market Cap @ EUR 100/share</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>€56,114 m</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>€56,114 m</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>€96,240 m</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>€95,300 m</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>€50,130 m</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The 2025 operating margin was calculated using EBIT divided by revenue as a proxy since EBIT margin was not reported explicitly. For Q1-2026, net liquidity, return on capital employed, and cost of capital are not available in the reported details.</t>
+          <t>The EBIT margin for the full year used the reported profit figures to compute the corresponding percentages, and the market cap was derived from shares outstanding.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>For the full year, the operating margin was derived from EBIT and revenue calculations due to lack of specific disclosure. EPS and dividend per share figures were not available for the full-year report, and the market cap was also not calculable due to absence of share counts.</t>
+          <t>All main figures were reported. Operating margin was computed for both periods based on disclosed EBIT and revenue, while market cap was derived. No cost of capital was available for Q1 2026.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>In the full year report, the 'cost of capital' and 'return on capital' metrics were not disclosed, so they are marked as 'N/A'. Dividend per share is reported, but market cap at 100 EUR/share is not available as share count information is not provided.</t>
+          <t>All metrics were directly reported with the exception of return_on_capital and cost_of_capital, which were not disclosed. Market cap @ 100 EUR/share was computed from shares outstanding.</t>
         </is>
       </c>
     </row>
@@ -1002,122 +1002,122 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[substituted]  Calculated as EBIT (Profit/loss before financial result) / Revenue.</t>
+          <t>[substituted] EBT Margin Computed in code: EBIT (€10,186 m) / Revenue (€133,453 m).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BMW Group — Net Liquidity / liquidity indicator (FY 2025)</t>
+          <t>BMW Group — Market Cap @ EUR 100/share (FY 2025)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] EUR 100 × shares outstanding Computed in code: EUR 100 × 561,135,000 shares.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BMW Group — Dividend per Share (FY 2025)</t>
+          <t>BMW Group — Operating Margin (EBIT margin / RoS) (Q1 2026)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] EBIT margin Computed in code: EBIT (€1,345 m) / Revenue (€31,007 m).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BMW Group — Market Cap @ EUR 100/share (FY 2025)</t>
+          <t>BMW Group — Return on Capital (value-based KPI) (Q1 2026)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[not_available]  Not reported in the quarterly report.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BMW Group — Net Liquidity / liquidity indicator (Q1 2026)</t>
+          <t>BMW Group — Cost of Capital / hurdle rate (Q1 2026)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[not_available]  Not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BMW Group — Return on Capital (value-based KPI) (Q1 2026)</t>
+          <t>BMW Group — Dividend per Share (Q1 2026)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[not_reported]  Dividends are typically proposed in the full-year report.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BMW Group — Cost of Capital / hurdle rate (Q1 2026)</t>
+          <t>BMW Group — Market Cap @ EUR 100/share (Q1 2026)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] EUR 100 × shares outstanding Computed in code: EUR 100 × 561,135,000 shares.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BMW Group — Dividend per Share (Q1 2026)</t>
+          <t>Mercedes-Benz Group — Operating Margin (EBIT margin / RoS) (FY 2025)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] EBIT / Revenue Computed in code: EBIT (€5,820 m) / Revenue (€132,214 m).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BMW Group — Market Cap @ EUR 100/share (Q1 2026)</t>
+          <t>Mercedes-Benz Group — Market Cap @ EUR 100/share (FY 2025)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] EUR 100 × shares outstanding Computed in code: EUR 100 × 962,400,000 shares.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group — Operating Margin (EBIT margin / RoS) (FY 2025)</t>
+          <t>Mercedes-Benz Group — Operating Margin (EBIT margin / RoS) (Q1 2026)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[substituted]  Calculated from EBIT (€5,820 m) / Revenue (€132,214 m) where margin data was not directly reported.</t>
+          <t>[substituted] EBIT / Revenue Computed in code: EBIT (€1,904 m) / Revenue (€31,602 m).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group — Earnings per Share (EPS) (FY 2025)</t>
+          <t>Mercedes-Benz Group — Cost of Capital / hurdle rate (Q1 2026)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1129,43 +1129,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group — Market Cap @ EUR 100/share (FY 2025)</t>
+          <t>Mercedes-Benz Group — Dividend per Share (Q1 2026)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[not_reported]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group — Operating Margin (EBIT margin / RoS) (Q1 2026)</t>
+          <t>Mercedes-Benz Group — Market Cap @ EUR 100/share (Q1 2026)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] EUR 100 × shares outstanding Computed in code: EUR 100 × 953,000,000 shares.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group — Cost of Capital / hurdle rate (Q1 2026)</t>
+          <t>Volkswagen Group — Operating Margin (EBIT margin / RoS) (FY 2025)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] Operative Umsatzrendite Computed in code: EBIT (€8,868 m) / Revenue (€321,913 m).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group — Dividend per Share (Q1 2026)</t>
+          <t>Volkswagen Group — Return on Capital (value-based KPI) (FY 2025)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group — Market Cap @ EUR 100/share (Q1 2026)</t>
+          <t>Volkswagen Group — Cost of Capital / hurdle rate (FY 2025)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1189,24 +1189,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Volkswagen Group — Cost of Capital / hurdle rate (FY 2025)</t>
+          <t>Volkswagen Group — Market Cap @ EUR 100/share (FY 2025)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] EUR 100 × shares outstanding Computed in code: EUR 100 × 501,295,263 shares.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Volkswagen Group — Market Cap @ EUR 100/share (FY 2025)</t>
+          <t>Volkswagen Group — Operating Margin (EBIT margin / RoS) (Q1 2026)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[substituted] Operative Umsatzrendite Computed in code: EBIT (€2,463 m) / Revenue (€75,657 m).</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[not_available]</t>
+          <t>[not_reported]</t>
         </is>
       </c>
     </row>
